--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:50:58+00:00</t>
+    <t>2026-04-14T12:43:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T12:43:47+00:00</t>
+    <t>2026-04-14T12:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T12:54:13+00:00</t>
+    <t>2026-04-14T12:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T12:53:30+00:00</t>
+    <t>2026-04-14T12:54:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T12:54:46+00:00</t>
+    <t>2026-04-14T12:55:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T12:55:07+00:00</t>
+    <t>2026-04-14T13:27:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T13:27:49+00:00</t>
+    <t>2026-04-14T13:29:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T13:29:17+00:00</t>
+    <t>2026-04-14T13:31:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T13:31:15+00:00</t>
+    <t>2026-04-15T09:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:18:52+00:00</t>
+    <t>2026-04-15T09:21:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:21:53+00:00</t>
+    <t>2026-04-15T09:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:25:45+00:00</t>
+    <t>2026-04-15T09:27:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:27:07+00:00</t>
+    <t>2026-04-15T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:28:43+00:00</t>
+    <t>2026-04-15T09:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:30:23+00:00</t>
+    <t>2026-04-15T09:41:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:41:07+00:00</t>
+    <t>2026-04-15T09:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:41:50+00:00</t>
+    <t>2026-04-15T09:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:43:29+00:00</t>
+    <t>2026-04-15T09:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:44:30+00:00</t>
+    <t>2026-04-15T09:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:46:03+00:00</t>
+    <t>2026-04-15T09:46:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:46:58+00:00</t>
+    <t>2026-04-15T09:49:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:49:42+00:00</t>
+    <t>2026-04-15T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
+++ b/conceptmaps-datatypes-part2/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T09:56:13+00:00</t>
+    <t>2026-04-20T09:24:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
